--- a/public/employee_upload_sample1.xlsx
+++ b/public/employee_upload_sample1.xlsx
@@ -1166,7 +1166,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:BJ1"/>
+  <x:dimension ref="A1:BL1"/>
   <x:sheetFormatPr defaultColWidth="8.996339" defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="13" width="8.996339" style="0" customWidth="1"/>
@@ -1181,6 +1181,7 @@
     <x:col min="57" max="57" width="10.571429" style="0" customWidth="1"/>
     <x:col min="58" max="62" width="8.996339" style="0" customWidth="1"/>
     <x:col min="63" max="63" width="18.710625" style="1" customWidth="1"/>
+    <x:col min="64" max="64" width="18.710625" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:63">
@@ -1378,6 +1379,11 @@
       </x:c>
       <x:c r="BK1" s="1" t="s">
         <x:v>59</x:v>
+      </x:c>
+      <x:c r="BL1" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Role</x:t>
+        </x:is>
       </x:c>
     </x:row>
   </x:sheetData>
